--- a/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>FEIT – Faculty of Engineering and Information Technology</t>
         </is>
@@ -652,649 +787,649 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="320" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+    <row r="16" ht="352" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
-This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
+This question also covers indicator EE1(c). Please note that this indicator will be addressed at the joint Associate Deans Sustainability and Associate Deans Teaching and Learning session on 23 November 2026. Please feel free to summarise what your faculty presented at this session - further information is welcome but not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>We have Associate Dean of Sustainability, and other sustainability-focused staff at different levels (varying between schools). We have also done the research which shows us proportion of courses with sustainability-related content. Within the FEIT strategic plan refresh the Deputy Dean of Academic and team have developed milestones and activities around sustainability to be included. To date a lot of the work is still in the planning phases - but it is an area of priority that we are hoping to advance further in 2026</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>https://eng.unimelb.edu.au/tll/news/the-spotllight/spotllight/spotllight-sustainability-education-and-the-future-of-engineering</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="188" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
 We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="303" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="270" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
-We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-    </row>
-    <row r="19" ht="286" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="K18" s="13" t="inlineStr"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="270" customHeight="1">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
-We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
+We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>We have a vast range of sustainability research taking place in FEIT - across all schools. There are numberous examples we can reference including the UMAMI project, mygreenlabs, and projects with World Bank that relate to sustainability. As we build connections through our FEIT Sustainability Community of Practice we learn of more and more work taking place in the area of sustainability, and through our recent survey asking staff which SDGs are relevant to them we also saw connections. We also identified 50+ PhD students working on sustainability related topics in FEIT</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="270" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
+      <c r="K19" s="13" t="inlineStr"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="237" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
-We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
+We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>We have a vast range of sustainability research taking place in FEIT - across all schools. There are numberous examples we can reference including the UMAMI project, mygreenlabs, and projects with World Bank that relate to sustainability. As we build connections through our FEIT Sustainability Community of Practice we learn of more and more work taking place in the area of sustainability, and through our recent survey asking staff which SDGs are relevant to them we also saw connections. We also identified 50+ PhD students working on sustainability related topics in FEIT</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="14" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="220" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="188" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
+In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>We have completed MyGreenLabs certification for one lab, and working to expand this certification to all FEIT labs. There is also work being undertaken to more efficiently manage materials such as chemicals to reduce wastage, and also general practice initiatives to reduce electrical use, such as turning off lights and monitors when not in use. We are also working on solutions to reduce required travel, and ways to further other operational behaviours like waste management.</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="14" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="220" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="188" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
+In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>We held a session - a panel discussion - as part of the 2025 National Indigenous Engineering Summit. This was organised in collboration with the FEIT Indigneous Engagement Portfolio team. The initiative centred Indigenous leadership and Caring for Country principles, strengthening how sustainability is understood and applied across engineering education and practice.</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
-      <c r="N22" s="14" t="n"/>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="14" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="254" customHeight="1">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="220" customHeight="1">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
-Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="188" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
+      <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="154" customHeight="1">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>We held four community of practice meetings in 2025, and also held a panel discussion event, part of the National Engineering Indigenous Summit, which included the sustainability commissioner of Victoria as a panel discussant. There is also the FEIT Sustainability in Education Community of Practice which focuses on embedding sustainability in practice and in learning, and developing ways to further integrate sustainability into the curriculum</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="14" t="n"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="15" t="n"/>
     </row>
     <row r="25"/>
   </sheetData>
@@ -1321,6 +1456,7 @@
     <hyperlink ref="H24" location="'3. SR25 responses'!B10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1330,7 +1466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1343,104 +1479,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1448,6 +1628,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1457,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1469,456 +1650,501 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Faculty of Engineering and Information Technology</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>FEIT</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Provide commentary with reference to data in the Flights dashboard (link in Column O) Based on data in the dashboard it appears FEIT will have similar data to 2024 - which is a reduction in emissions from 2023 - however the 2025 data may not show a decrease/improvement from 2024 - indicating a need to focus further on reducing our emissions from flights within the Faculty. In Q2 and Q3 FEIT exceeeded the emissions of 2024 - while Q1 was less than 2025.</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>We are continuing to develop an action plan through our Community of Practice to address GHG emissions from flights and develop actionable strategies to reduce our emissions</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>We currently have 60 members of the FEIT Sustainability Community of Practice, meeting quarterly. Work continues to identify and engage staff and students involved in sustainability to join our network. We also conducted a survey this year to identify staff working on a sustainability theme - aligned with the SDGs, and they indicated which SDGs are relevant to their work. We were able to graph this data based on schools within the Faculty.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>We held four community of practice meetings in 2025, and also held a panel discussion event, part of the National Engineering Indigenous Summit, which included the sustainability commissioner of Victoria as a panel discussant. There is also the FEIT Sustainability in Education Community of Practice which focuses on embedding sustainability in practice and in learning, and developing ways to further integrate sustainability into the curriculum</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="188" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>We don't yet have data on FEIT staff that have undertaken the Sustainability @ Melbourne training - but that is something we will explore. There is good participation in the FEIT Sustainability Community of Practice and also the FEIT Sustainability in Education Community of Practice and the activities associated with those groups. No formal training has been developed yet, however there is different initiatives in the planning stages.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="12" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>We have Associate Dean of Sustainability, and other sustainability-focused staff at different levels (varying between schools). We have also done the research which shows us proportion of courses with sustainability-related content. Within the FEIT strategic plan refresh the Deputy Dean of Academic and team have developed milestones and activities around sustainability to be included. To date a lot of the work is still in the planning phases - but it is an area of priority that we are hoping to advance further in 2026</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>https://eng.unimelb.edu.au/tll/news/the-spotllight/spotllight/spotllight-sustainability-education-and-the-future-of-engineering</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead 
 and succeed in the careers, communities and industries 
 of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Sustainability content is present in FEIT courses</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>Yes, we have measured subjects - put in sustainability in the curriculum data. We can go further and get feedback from graduates regarding their sustainability self-efficacy.</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="171" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>We have a vast range of sustainability research taking place in FEIT - across all schools. There are numberous examples we can reference including the UMAMI project, mygreenlabs, and projects with World Bank that relate to sustainability. As we build connections through our FEIT Sustainability Community of Practice we learn of more and more work taking place in the area of sustainability, and through our recent survey asking staff which SDGs are relevant to them we also saw connections. We also identified 50+ PhD students working on sustainability related topics in FEIT</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr"/>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="160" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>We have completed MyGreenLabs certification for one lab, and working to expand this certification to all FEIT labs. There is also work being undertaken to more efficiently manage materials such as chemicals to reduce wastage, and also general practice initiatives to reduce electrical use, such as turning off lights and monitors when not in use. We are also working on solutions to reduce required travel, and ways to further other operational behaviours like waste management.</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="160" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>We held a session - a panel discussion - as part of the 2025 National Indigenous Engineering Summit. This was organised in collboration with the FEIT Indigneous Engagement Portfolio team. The initiative centred Indigenous leadership and Caring for Country principles, strengthening how sustainability is understood and applied across engineering education and practice.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="160" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>7b</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>The University has led or influenced discussions with precinct partners to further precinct-specific approaches to sustainability</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>If the Faculty is located in a precinct (FEIT, FFAM, MDHS), describe the Faculty's involvement in sustainability issues for that precinct. If the faculty is not located in a precinct, please skip this indicator.</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>We have successfully gained ceritifcation for one lab with MyGreenLabs in Melbourne Connect, and will continue to work to certify other labs within FEIT. We are also working to improve a number of other relevant operations such as waste management, and electricity usage.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1928,6 +2154,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -988,45 +988,55 @@
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="15" t="n"/>
     </row>
-    <row r="17" ht="188" customHeight="1">
+    <row r="17" ht="270" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>EE1(b)</t>
+          <t>TR1(a)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Exceptional education</t>
+          <t>Transformational research</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
+          <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
+          <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
-We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
+          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>N/A – new indicator</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr"/>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>2a
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
+        </is>
+      </c>
       <c r="K17" s="13" t="inlineStr"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
@@ -1038,7 +1048,7 @@
     <row r="18" ht="270" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>TR1(a)</t>
+          <t>TR2(a)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -1048,29 +1058,29 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
+          <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
+          <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
-Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
-In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
+We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>2a
+          <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
@@ -1081,7 +1091,7 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
+          <t>We have a vast range of sustainability research taking place in FEIT - across all schools. There are numberous examples we can reference including the UMAMI project, mygreenlabs, and projects with World Bank that relate to sustainability. As we build connections through our FEIT Sustainability Community of Practice we learn of more and more work taking place in the area of sustainability, and through our recent survey asking staff which SDGs are relevant to them we also saw connections. We also identified 50+ PhD students working on sustainability related topics in FEIT</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr"/>
@@ -1092,10 +1102,10 @@
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
     </row>
-    <row r="19" ht="270" customHeight="1">
+    <row r="19" ht="237" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>TR2(a)</t>
+          <t>TR2(d)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1110,19 +1120,19 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
+          <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
-We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
+We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
 In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
+          <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -1149,10 +1159,10 @@
       <c r="P19" s="15" t="n"/>
       <c r="Q19" s="15" t="n"/>
     </row>
-    <row r="20" ht="237" customHeight="1">
+    <row r="20" ht="188" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>TR2(d)</t>
+          <t>TR3(b)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -1162,29 +1172,28 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
+          <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
+          <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
-We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
-In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
+In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
+          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>5b(i)
+          <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
@@ -1195,7 +1204,7 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>We have a vast range of sustainability research taking place in FEIT - across all schools. There are numberous examples we can reference including the UMAMI project, mygreenlabs, and projects with World Bank that relate to sustainability. As we build connections through our FEIT Sustainability Community of Practice we learn of more and more work taking place in the area of sustainability, and through our recent survey asking staff which SDGs are relevant to them we also saw connections. We also identified 50+ PhD students working on sustainability related topics in FEIT</t>
+          <t>We have completed MyGreenLabs certification for one lab, and working to expand this certification to all FEIT labs. There is also work being undertaken to more efficiently manage materials such as chemicals to reduce wastage, and also general practice initiatives to reduce electrical use, such as turning off lights and monitors when not in use. We are also working on solutions to reduce required travel, and ways to further other operational behaviours like waste management.</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr"/>
@@ -1209,38 +1218,38 @@
     <row r="21" ht="188" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>TR3(b)</t>
+          <t>EN1(a)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Transformational research</t>
+          <t>Enablers</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
+          <t>Enablers</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
+          <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
-In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
+In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
+          <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>5c(ii)
+          <t>6a
 → view SR25 response</t>
         </is>
       </c>
@@ -1251,7 +1260,7 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>We have completed MyGreenLabs certification for one lab, and working to expand this certification to all FEIT labs. There is also work being undertaken to more efficiently manage materials such as chemicals to reduce wastage, and also general practice initiatives to reduce electrical use, such as turning off lights and monitors when not in use. We are also working on solutions to reduce required travel, and ways to further other operational behaviours like waste management.</t>
+          <t>We held a session - a panel discussion - as part of the 2025 National Indigenous Engineering Summit. This was organised in collboration with the FEIT Indigneous Engagement Portfolio team. The initiative centred Indigenous leadership and Caring for Country principles, strengthening how sustainability is understood and applied across engineering education and practice.</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr"/>
@@ -1262,10 +1271,10 @@
       <c r="P21" s="15" t="n"/>
       <c r="Q21" s="15" t="n"/>
     </row>
-    <row r="22" ht="188" customHeight="1">
+    <row r="22" ht="220" customHeight="1">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>EN1(a)</t>
+          <t>EN1(b)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -1280,23 +1289,24 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
+          <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
-In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
+          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>6a
+          <t>2a
 → view SR25 response</t>
         </is>
       </c>
@@ -1307,7 +1317,7 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>We held a session - a panel discussion - as part of the 2025 National Indigenous Engineering Summit. This was organised in collboration with the FEIT Indigneous Engagement Portfolio team. The initiative centred Indigenous leadership and Caring for Country principles, strengthening how sustainability is understood and applied across engineering education and practice.</t>
+          <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr"/>
@@ -1318,10 +1328,10 @@
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
     </row>
-    <row r="23" ht="220" customHeight="1">
+    <row r="23" ht="154" customHeight="1">
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>EN1(b)</t>
+          <t>EN1(c)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -1336,24 +1346,23 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
+          <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
-Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
-In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
+          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>2a
+          <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
@@ -1364,7 +1373,7 @@
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>We have a number of examples of living labs in FEIT, from our sensors monitoring building usage, health and quality, to the MyGreenLabs certification, as well as our FEIT Community of Practice initiatives, and a number of other projects such as the sustainability self-efficacy measurement tool, and the UMAMI project which developed an AI tool for discovering data and insights about our campus to support sustainability and retrofit decisions.</t>
+          <t>We held four community of practice meetings in 2025, and also held a panel discussion event, part of the National Engineering Indigenous Summit, which included the sustainability commissioner of Victoria as a panel discussant. There is also the FEIT Sustainability in Education Community of Practice which focuses on embedding sustainability in practice and in learning, and developing ways to further integrate sustainability into the curriculum</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr"/>
@@ -1375,63 +1384,7 @@
       <c r="P23" s="15" t="n"/>
       <c r="Q23" s="15" t="n"/>
     </row>
-    <row r="24" ht="154" customHeight="1">
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>EN1(c)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Enablers</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Enablers</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
-In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>3a(ii)
-→ view SR25 response</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>We held four community of practice meetings in 2025, and also held a panel discussion event, part of the National Engineering Indigenous Summit, which included the sustainability commissioner of Victoria as a panel discussant. There is also the FEIT Sustainability in Education Community of Practice which focuses on embedding sustainability in practice and in learning, and developing ways to further integrate sustainability into the curriculum</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
+    <row r="24"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
@@ -1441,19 +1394,19 @@
     <mergeCell ref="B4:C8"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="P16:P24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+    <dataValidation sqref="P16:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
-    <hyperlink ref="H18" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H18" location="'3. SR25 responses'!B14"/>
     <hyperlink ref="H19" location="'3. SR25 responses'!B14"/>
-    <hyperlink ref="H20" location="'3. SR25 responses'!B14"/>
-    <hyperlink ref="H21" location="'3. SR25 responses'!B15"/>
-    <hyperlink ref="H22" location="'3. SR25 responses'!B16"/>
-    <hyperlink ref="H23" location="'3. SR25 responses'!B8"/>
-    <hyperlink ref="H24" location="'3. SR25 responses'!B10"/>
+    <hyperlink ref="H20" location="'3. SR25 responses'!B15"/>
+    <hyperlink ref="H21" location="'3. SR25 responses'!B16"/>
+    <hyperlink ref="H22" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H23" location="'3. SR25 responses'!B10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FEIT - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -985,8 +966,6 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="270" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -1042,8 +1021,6 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="270" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
@@ -1099,8 +1076,6 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19" ht="237" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
@@ -1156,8 +1131,6 @@
       <c r="M19" s="15" t="n"/>
       <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
     </row>
     <row r="20" ht="188" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
@@ -1212,8 +1185,6 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
     </row>
     <row r="21" ht="188" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
@@ -1268,8 +1239,6 @@
       <c r="M21" s="15" t="n"/>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="15" t="n"/>
     </row>
     <row r="22" ht="220" customHeight="1">
       <c r="B22" s="11" t="inlineStr">
@@ -1325,8 +1294,6 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="15" t="n"/>
     </row>
     <row r="23" ht="154" customHeight="1">
       <c r="B23" s="11" t="inlineStr">
@@ -1351,13 +1318,13 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a sustainability outcome.
 In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1381,23 +1348,16 @@
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
-      <c r="P23" s="15" t="n"/>
-      <c r="Q23" s="15" t="n"/>
     </row>
     <row r="24"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
     <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
